--- a/tests/data_golden/layout.expected.xlsx
+++ b/tests/data_golden/layout.expected.xlsx
@@ -88,13 +88,13 @@
     <t>apple</t>
   </si>
   <si>
-    <t>red fruit</t>
+    <t xml:space="preserve">red fruit</t>
   </si>
   <si>
     <t>banana</t>
   </si>
   <si>
-    <t>yellow fruit</t>
+    <t xml:space="preserve">yellow fruit</t>
   </si>
   <si>
     <t>Q1</t>
